--- a/docs/Decodifiche/152_dmnm_dec_tipo_cert_morte.xlsx
+++ b/docs/Decodifiche/152_dmnm_dec_tipo_cert_morte.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -35,10 +35,7 @@
     <t>Certificazione originaria</t>
   </si>
   <si>
-    <t>2024-10-30 00:00:00.0</t>
-  </si>
-  <si>
-    <t>9999-12-31 00:00:00.0</t>
+    <t/>
   </si>
   <si>
     <t>1</t>
@@ -120,8 +117,8 @@
   <cols>
     <col min="1" max="1" width="3.02734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="22.26171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="21.33984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.33984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.4921875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.86328125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.55859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -153,61 +150,61 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
